--- a/CV_PowerBI.xlsx
+++ b/CV_PowerBI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bertelsmann-my.sharepoint.com/personal/tristan_strothmann_embrace_agency/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e259af606cbf7e0/Daten Analyse/_Bewerbungs_Bericht/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{83B984C8-23B1-4AFB-AFEB-B45E9C107294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{645E73BA-3853-43B2-84DF-F3FF59079E6F}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="8_{83B984C8-23B1-4AFB-AFEB-B45E9C107294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCC21286-6406-455F-A2AC-A72600AB352D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C70C9C52-B270-442F-BC68-4AC66DB2DCB0}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="47">
   <si>
     <t>Monat</t>
   </si>
@@ -538,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{919ED4E1-D25D-49D1-85A2-A6F1BC3C4AC5}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="37.5703125" bestFit="1" customWidth="1"/>
@@ -1023,6 +1023,26 @@
         <v>33</v>
       </c>
       <c r="F24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2026</v>
+      </c>
+      <c r="B25">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" t="s">
         <v>34</v>
       </c>
     </row>
